--- a/output/Test_Cases_collection/TC06 - Checkout with Valid Information.xlsx
+++ b/output/Test_Cases_collection/TC06 - Checkout with Valid Information.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -70,25 +70,37 @@
     <t>9</t>
   </si>
   <si>
-    <t>Launch the application and open [https://www.saucedemo.com/]</t>
-  </si>
-  <si>
-    <t>Log in with valid credentials ("standard_user" and "secret_sauce")</t>
-  </si>
-  <si>
-    <t>Add "Sauce Labs Backpack" to the cart</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Launch the application and open https://www.saucedemo.com/</t>
+  </si>
+  <si>
+    <t>Enter "standard_user" in the "user-name" field</t>
+  </si>
+  <si>
+    <t>Enter "secret_sauce" in the "password" field</t>
+  </si>
+  <si>
+    <t>Click on "login-button"</t>
+  </si>
+  <si>
+    <t>Click on "add-to-cart-sauce-labs-backpack"</t>
   </si>
   <si>
     <t>Click on "checkout"</t>
   </si>
   <si>
-    <t>Enter "test" in the "firstName" field</t>
+    <t>Enter "testqt" in the "firstName" field</t>
   </si>
   <si>
     <t>Enter "test" in the "lastName" field</t>
   </si>
   <si>
-    <t>Enter "76565" in the "postalCode" field</t>
+    <t>Enter "23214323" in the "postalCode" field</t>
   </si>
   <si>
     <t>Click on "continue"</t>
@@ -97,37 +109,43 @@
     <t>Click on "finish"</t>
   </si>
   <si>
-    <t>Verify the order confirmation message</t>
-  </si>
-  <si>
-    <t>Application is launched successfully</t>
-  </si>
-  <si>
-    <t>User is redirected to [https://www.saucedemo.com/inventory.html]</t>
-  </si>
-  <si>
-    <t>Item is added to the cart successfully</t>
-  </si>
-  <si>
-    <t>User is redirected to [https://www.saucedemo.com/checkout-step-one.html]</t>
-  </si>
-  <si>
-    <t>First name is entered successfully</t>
-  </si>
-  <si>
-    <t>Last name is entered successfully</t>
-  </si>
-  <si>
-    <t>Postal code is entered successfully</t>
-  </si>
-  <si>
-    <t>User is redirected to [https://www.saucedemo.com/checkout-step-two.html]</t>
-  </si>
-  <si>
-    <t>User is redirected to [https://www.saucedemo.com/checkout-complete.html]</t>
-  </si>
-  <si>
-    <t>"Thank you for your order! Your order has been dispatched, and will arrive just as fast as the pony can get there!" is displayed</t>
+    <t>Verify the message "Thank you for your order!"</t>
+  </si>
+  <si>
+    <t>Application is launched, and the login page is displayed.</t>
+  </si>
+  <si>
+    <t>Username is entered successfully.</t>
+  </si>
+  <si>
+    <t>Password is entered successfully.</t>
+  </si>
+  <si>
+    <t>User is redirected to the inventory page at https://www.saucedemo.com/inventory.html.</t>
+  </si>
+  <si>
+    <t>"1" is displayed in the cart icon.</t>
+  </si>
+  <si>
+    <t>User is redirected to the checkout step one page at https://www.saucedemo.com/checkout-step-one.html.</t>
+  </si>
+  <si>
+    <t>First name is entered successfully.</t>
+  </si>
+  <si>
+    <t>Last name is entered successfully.</t>
+  </si>
+  <si>
+    <t>Postal code is entered successfully.</t>
+  </si>
+  <si>
+    <t>User is redirected to the checkout step two page at https://www.saucedemo.com/checkout-step-two.html.</t>
+  </si>
+  <si>
+    <t>User is redirected to the checkout complete page at https://www.saucedemo.com/checkout-complete.html.</t>
+  </si>
+  <si>
+    <t>Confirmation message is displayed.</t>
   </si>
   <si>
     <t>New</t>
@@ -494,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -528,19 +546,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -551,16 +569,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -571,16 +589,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -591,16 +609,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -611,16 +629,16 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -631,16 +649,16 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -651,16 +669,16 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -671,16 +689,16 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -691,16 +709,16 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -711,16 +729,56 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output/Test_Cases_collection/TC06 - Checkout with Valid Information.xlsx
+++ b/output/Test_Cases_collection/TC06 - Checkout with Valid Information.xlsx
@@ -76,13 +76,13 @@
     <t>11</t>
   </si>
   <si>
-    <t>Launch the application and open https://www.saucedemo.com/</t>
-  </si>
-  <si>
-    <t>Enter "standard_user" in the "user-name" field</t>
-  </si>
-  <si>
-    <t>Enter "secret_sauce" in the "password" field</t>
+    <t>Launch the application and open [https://www.saucedemo.com/]</t>
+  </si>
+  <si>
+    <t>Enter "standard_user" in "user-name" field</t>
+  </si>
+  <si>
+    <t>Enter "secret_sauce" in "password" field</t>
   </si>
   <si>
     <t>Click on "login-button"</t>
@@ -94,13 +94,13 @@
     <t>Click on "checkout"</t>
   </si>
   <si>
-    <t>Enter "testqt" in the "firstName" field</t>
-  </si>
-  <si>
-    <t>Enter "test" in the "lastName" field</t>
-  </si>
-  <si>
-    <t>Enter "23214323" in the "postalCode" field</t>
+    <t>Enter "test" in "firstName" field</t>
+  </si>
+  <si>
+    <t>Enter "test" in "lastName" field</t>
+  </si>
+  <si>
+    <t>Enter "12345" in "postalCode" field</t>
   </si>
   <si>
     <t>Click on "continue"</t>
@@ -109,43 +109,43 @@
     <t>Click on "finish"</t>
   </si>
   <si>
-    <t>Verify the message "Thank you for your order!"</t>
-  </si>
-  <si>
-    <t>Application is launched, and the login page is displayed.</t>
-  </si>
-  <si>
-    <t>Username is entered successfully.</t>
-  </si>
-  <si>
-    <t>Password is entered successfully.</t>
-  </si>
-  <si>
-    <t>User is redirected to the inventory page at https://www.saucedemo.com/inventory.html.</t>
-  </si>
-  <si>
-    <t>"1" is displayed in the cart icon.</t>
-  </si>
-  <si>
-    <t>User is redirected to the checkout step one page at https://www.saucedemo.com/checkout-step-one.html.</t>
-  </si>
-  <si>
-    <t>First name is entered successfully.</t>
-  </si>
-  <si>
-    <t>Last name is entered successfully.</t>
-  </si>
-  <si>
-    <t>Postal code is entered successfully.</t>
-  </si>
-  <si>
-    <t>User is redirected to the checkout step two page at https://www.saucedemo.com/checkout-step-two.html.</t>
-  </si>
-  <si>
-    <t>User is redirected to the checkout complete page at https://www.saucedemo.com/checkout-complete.html.</t>
-  </si>
-  <si>
-    <t>Confirmation message is displayed.</t>
+    <t>Verify the message "Thank you for your order!" is displayed</t>
+  </si>
+  <si>
+    <t>Application is launched, and the login page is displayed</t>
+  </si>
+  <si>
+    <t>Username is entered successfully</t>
+  </si>
+  <si>
+    <t>Password is entered successfully</t>
+  </si>
+  <si>
+    <t>User is redirected to the inventory page [https://www.saucedemo.com/inventory.html]</t>
+  </si>
+  <si>
+    <t>Product is added to the cart, and the cart icon shows "1"</t>
+  </si>
+  <si>
+    <t>User is redirected to the checkout step one page [https://www.saucedemo.com/checkout-step-one.html]</t>
+  </si>
+  <si>
+    <t>First name is entered successfully</t>
+  </si>
+  <si>
+    <t>Last name is entered successfully</t>
+  </si>
+  <si>
+    <t>Postal code is entered successfully</t>
+  </si>
+  <si>
+    <t>User is redirected to the checkout step two page [https://www.saucedemo.com/checkout-step-two.html]</t>
+  </si>
+  <si>
+    <t>User is redirected to the checkout complete page [https://www.saucedemo.com/checkout-complete.html]</t>
+  </si>
+  <si>
+    <t>Order confirmation message is displayed successfully</t>
   </si>
   <si>
     <t>New</t>
